--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_4.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01763543263008518</v>
+        <v>0.01140174178467683</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008411541098893133</v>
+        <v>0.00840949336849749</v>
       </c>
       <c r="C2" t="n">
-        <v>25452324</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25452324</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>18419496</v>
+        <v>4517897</v>
       </c>
       <c r="L2" t="n">
-        <v>10605239</v>
+        <v>2507898</v>
       </c>
       <c r="M2" t="n">
-        <v>2681304</v>
+        <v>615074</v>
       </c>
       <c r="N2" t="n">
-        <v>150637</v>
+        <v>29982</v>
       </c>
       <c r="O2" t="n">
-        <v>1611566</v>
+        <v>380630</v>
       </c>
       <c r="P2" t="n">
-        <v>650098</v>
+        <v>154045</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999886155128479</v>
+        <v>0.9999889731407166</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9014421701431274</v>
+        <v>0.8780410289764404</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8017778396606445</v>
+        <v>0.7646251916885376</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7377901077270508</v>
+        <v>0.6998224854469299</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5153189301490784</v>
+        <v>0.4131288528442383</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7928820252418518</v>
+        <v>0.7532022595405579</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8502781391143799</v>
+        <v>0.8220336437225342</v>
       </c>
       <c r="X2" t="n">
-        <v>25452324</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25452324</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>19453918</v>
+        <v>4843813</v>
       </c>
       <c r="AG2" t="n">
-        <v>11974836</v>
+        <v>2988574</v>
       </c>
       <c r="AH2" t="n">
-        <v>3208013</v>
+        <v>801351</v>
       </c>
       <c r="AI2" t="n">
-        <v>236747</v>
+        <v>59120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1837712</v>
+        <v>459465</v>
       </c>
       <c r="AK2" t="n">
-        <v>720176</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565864205360413</v>
+        <v>0.9564417004585266</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113011956214905</v>
+        <v>0.9113976359367371</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8579807281494141</v>
+        <v>0.8579177856445312</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6621256470680237</v>
+        <v>0.6617860794067383</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019365906715393</v>
+        <v>0.9019746780395508</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.93143230676651</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.00426638111091527</v>
+        <v>0.00267143148735529</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002015256325970591</v>
+        <v>0.002015272774735009</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>18419496</v>
+        <v>4517897</v>
       </c>
       <c r="E3" t="n">
-        <v>1835705</v>
+        <v>530706</v>
       </c>
       <c r="F3" t="n">
-        <v>47052</v>
+        <v>8182</v>
       </c>
       <c r="G3" t="n">
-        <v>10334</v>
+        <v>1031</v>
       </c>
       <c r="H3" t="n">
-        <v>2025</v>
+        <v>404</v>
       </c>
       <c r="I3" t="n">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="J3" t="n">
-        <v>40384186</v>
+        <v>10069550</v>
       </c>
       <c r="K3" t="n">
-        <v>43508152</v>
+        <v>10730209</v>
       </c>
       <c r="L3" t="n">
-        <v>50055738</v>
+        <v>12359457</v>
       </c>
       <c r="M3" t="n">
-        <v>61142708</v>
+        <v>15217654</v>
       </c>
       <c r="N3" t="n">
-        <v>65337339</v>
+        <v>16284036</v>
       </c>
       <c r="O3" t="n">
-        <v>63377536</v>
+        <v>15781696</v>
       </c>
       <c r="P3" t="n">
-        <v>64949005</v>
+        <v>16189304</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9067041873931885</v>
+        <v>0.8931721448898315</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8059214353561401</v>
+        <v>0.7635471224784851</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7167041301727295</v>
+        <v>0.6581710577011108</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4210324883460999</v>
+        <v>0.33547043800354</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7906468510627747</v>
+        <v>0.7469411492347717</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8406562805175781</v>
+        <v>0.7967323064804077</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19453918</v>
+        <v>4843813</v>
       </c>
       <c r="Z3" t="n">
-        <v>798777</v>
+        <v>198937</v>
       </c>
       <c r="AA3" t="n">
-        <v>34422</v>
+        <v>8593</v>
       </c>
       <c r="AB3" t="n">
-        <v>27363</v>
+        <v>6842</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40384476</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>44639126</v>
+        <v>11137143</v>
       </c>
       <c r="AG3" t="n">
-        <v>51512118</v>
+        <v>12840927</v>
       </c>
       <c r="AH3" t="n">
-        <v>61564627</v>
+        <v>15348766</v>
       </c>
       <c r="AI3" t="n">
-        <v>65358211</v>
+        <v>16296413</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63598706</v>
+        <v>15856481</v>
       </c>
       <c r="AK3" t="n">
-        <v>65010462</v>
+        <v>16209400</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576238393783569</v>
+        <v>0.9576045870780945</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100009202957153</v>
+        <v>0.9098923206329346</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8574917316436768</v>
+        <v>0.8575001358985901</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6617110967636108</v>
+        <v>0.6614972949028015</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015958309173584</v>
+        <v>0.9016454815864563</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312757253646851</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.04969400971406237</v>
+        <v>0.03515697859605242</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03184854034087193</v>
+        <v>0.031840082348875</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1909196</v>
+        <v>595808</v>
       </c>
       <c r="E4" t="n">
-        <v>10605239</v>
+        <v>2507898</v>
       </c>
       <c r="F4" t="n">
-        <v>581074</v>
+        <v>162351</v>
       </c>
       <c r="G4" t="n">
-        <v>20774</v>
+        <v>5420</v>
       </c>
       <c r="H4" t="n">
-        <v>39367</v>
+        <v>12048</v>
       </c>
       <c r="I4" t="n">
-        <v>3480</v>
+        <v>1008</v>
       </c>
       <c r="J4" t="n">
-        <v>290</v>
+        <v>70</v>
       </c>
       <c r="K4" t="n">
-        <v>2013868</v>
+        <v>627531</v>
       </c>
       <c r="L4" t="n">
-        <v>2621915</v>
+        <v>772007</v>
       </c>
       <c r="M4" t="n">
-        <v>952933</v>
+        <v>263826</v>
       </c>
       <c r="N4" t="n">
-        <v>141681</v>
+        <v>42591</v>
       </c>
       <c r="O4" t="n">
-        <v>420976</v>
+        <v>124719</v>
       </c>
       <c r="P4" t="n">
-        <v>114473</v>
+        <v>33350</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999943375587463</v>
+        <v>0.9999944567680359</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9040654897689819</v>
+        <v>0.8855419754981995</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8038443326950073</v>
+        <v>0.7640858292579651</v>
       </c>
       <c r="T4" t="n">
-        <v>0.727094292640686</v>
+        <v>0.6783580183982849</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4634286165237427</v>
+        <v>0.3702715635299683</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7917628884315491</v>
+        <v>0.750058650970459</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8454398512840271</v>
+        <v>0.809185266494751</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>824373</v>
+        <v>205971</v>
       </c>
       <c r="Z4" t="n">
-        <v>11974836</v>
+        <v>2988574</v>
       </c>
       <c r="AA4" t="n">
-        <v>332978</v>
+        <v>83251</v>
       </c>
       <c r="AB4" t="n">
-        <v>22096</v>
+        <v>5524</v>
       </c>
       <c r="AC4" t="n">
-        <v>4592</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>882894</v>
+        <v>220597</v>
       </c>
       <c r="AG4" t="n">
-        <v>1165535</v>
+        <v>290537</v>
       </c>
       <c r="AH4" t="n">
-        <v>531014</v>
+        <v>132714</v>
       </c>
       <c r="AI4" t="n">
-        <v>120809</v>
+        <v>30214</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199806</v>
+        <v>49934</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571048021316528</v>
+        <v>0.9570227861404419</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106505513191223</v>
+        <v>0.9106442928314209</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577361702919006</v>
+        <v>0.8577089309692383</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6619182825088501</v>
+        <v>0.6616416573524475</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017662405967712</v>
+        <v>0.9018100500106812</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313539862632751</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>64482</v>
+        <v>19871</v>
       </c>
       <c r="E5" t="n">
-        <v>690715</v>
+        <v>209786</v>
       </c>
       <c r="F5" t="n">
-        <v>2681304</v>
+        <v>615074</v>
       </c>
       <c r="G5" t="n">
-        <v>58422</v>
+        <v>18132</v>
       </c>
       <c r="H5" t="n">
-        <v>229958</v>
+        <v>66629</v>
       </c>
       <c r="I5" t="n">
-        <v>16273</v>
+        <v>5027</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1895284</v>
+        <v>540363</v>
       </c>
       <c r="L5" t="n">
-        <v>2553908</v>
+        <v>776638</v>
       </c>
       <c r="M5" t="n">
-        <v>1059855</v>
+        <v>319446</v>
       </c>
       <c r="N5" t="n">
-        <v>207143</v>
+        <v>59391</v>
       </c>
       <c r="O5" t="n">
-        <v>426722</v>
+        <v>128955</v>
       </c>
       <c r="P5" t="n">
-        <v>123224</v>
+        <v>39301</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999955892562866</v>
+        <v>0.9999957084655762</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9406235814094543</v>
+        <v>0.928856372833252</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9213840365409851</v>
+        <v>0.905662477016449</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9694275856018066</v>
+        <v>0.964469313621521</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9947016835212708</v>
+        <v>0.9937876462936401</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9871242642402649</v>
+        <v>0.9845471382141113</v>
       </c>
       <c r="W5" t="n">
-        <v>0.996389627456665</v>
+        <v>0.9955743551254272</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32300</v>
+        <v>8071</v>
       </c>
       <c r="Z5" t="n">
-        <v>341661</v>
+        <v>85325</v>
       </c>
       <c r="AA5" t="n">
-        <v>3208013</v>
+        <v>801351</v>
       </c>
       <c r="AB5" t="n">
-        <v>39915</v>
+        <v>9981</v>
       </c>
       <c r="AC5" t="n">
-        <v>116738</v>
+        <v>29159</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>860862</v>
+        <v>214447</v>
       </c>
       <c r="AG5" t="n">
-        <v>1184311</v>
+        <v>295962</v>
       </c>
       <c r="AH5" t="n">
-        <v>533146</v>
+        <v>133169</v>
       </c>
       <c r="AI5" t="n">
-        <v>121033</v>
+        <v>30253</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200576</v>
+        <v>50120</v>
       </c>
       <c r="AK5" t="n">
-        <v>53146</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735139608383179</v>
+        <v>0.9734987616539001</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643080234527588</v>
+        <v>0.9642727375030518</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838364124298096</v>
+        <v>0.9838034510612488</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963266253471375</v>
+        <v>0.9963165521621704</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939185976982117</v>
+        <v>0.9939050674438477</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983875155448914</v>
+        <v>0.9983825087547302</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>39687</v>
+        <v>11803</v>
       </c>
       <c r="E6" t="n">
-        <v>52436</v>
+        <v>18070</v>
       </c>
       <c r="F6" t="n">
-        <v>71252</v>
+        <v>18009</v>
       </c>
       <c r="G6" t="n">
-        <v>150637</v>
+        <v>29982</v>
       </c>
       <c r="H6" t="n">
-        <v>39664</v>
+        <v>10325</v>
       </c>
       <c r="I6" t="n">
-        <v>4060</v>
+        <v>1167</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25997</v>
+        <v>6499</v>
       </c>
       <c r="Z6" t="n">
-        <v>21526</v>
+        <v>5384</v>
       </c>
       <c r="AA6" t="n">
-        <v>43617</v>
+        <v>10901</v>
       </c>
       <c r="AB6" t="n">
-        <v>236747</v>
+        <v>59120</v>
       </c>
       <c r="AC6" t="n">
-        <v>27969</v>
+        <v>6988</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>423</v>
+        <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>40960</v>
+        <v>12845</v>
       </c>
       <c r="F7" t="n">
-        <v>245442</v>
+        <v>72824</v>
       </c>
       <c r="G7" t="n">
-        <v>49330</v>
+        <v>17144</v>
       </c>
       <c r="H7" t="n">
-        <v>1611566</v>
+        <v>380630</v>
       </c>
       <c r="I7" t="n">
-        <v>90500</v>
+        <v>26112</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3247</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118676</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30373</v>
+        <v>7601</v>
       </c>
       <c r="AC7" t="n">
-        <v>1837712</v>
+        <v>459465</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>149</v>
+        <v>41</v>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>2099</v>
+        <v>600</v>
       </c>
       <c r="F8" t="n">
-        <v>8113</v>
+        <v>2460</v>
       </c>
       <c r="G8" t="n">
-        <v>2821</v>
+        <v>864</v>
       </c>
       <c r="H8" t="n">
-        <v>109962</v>
+        <v>35313</v>
       </c>
       <c r="I8" t="n">
-        <v>650098</v>
+        <v>154045</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1321</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1062</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50327</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720176</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
